--- a/quizzes/peinture-14e.xlsx
+++ b/quizzes/peinture-14e.xlsx
@@ -526,52 +526,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg/960px-An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ahmad</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MUSA</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7a/Wilton_diptych.jpg/1280px-Wilton_diptych.jpg</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MAÎTRE DU DIPTYQUE DE WILTON</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1395-1399</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Bibliothèque du Topkapi</t>
+          <t>National Gallery</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>"Un ange offre une ville au Prophète"</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>"Miraj Nameh"</t>
+          <t>"Le Diptyque Wilton"</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>"The Wilton Diptych"</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Encre, couleurs et or sur papier</t>
+          <t>Tempera sur bois</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>53 cm</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>37 cm</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>persane</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -581,62 +586,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/68/Padova%2C_basilica_di_Sant%27Antonio_-_Cappella_di_San_Giacomo_-_Affreschi_03.jpg/1280px-Padova%2C_basilica_di_Sant%27Antonio_-_Cappella_di_San_Giacomo_-_Affreschi_03.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/Feofan_Grek_-_Madonna_of_Don_Icon_-_WGA22207.jpg/1280px-Feofan_Grek_-_Madonna_of_Don_Icon_-_WGA22207.jpg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Altichiero</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>da ZEVIO</t>
+          <t>Théophane</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LE GREC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>environ 1330</t>
+          <t>environ 1340</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>environ 1390</t>
+          <t>environ 1410</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1372-1379</t>
+          <t>1382-1395</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Padoue</t>
+          <t>Moscou</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Basilique Saint-Antoine</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Chapelle San Giacomo</t>
+          <t>Galerie Tretiakov</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>"Fresques"</t>
+          <t>"Icône Notre-Dame du Don"</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fresque</t>
+          <t>Tempera sur bois</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>grecque</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -646,52 +646,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Ambrogio_Lorenzetti_-_Effects_of_Good_Government_in_the_city_-_Google_Art_Project.jpg/1280px-Ambrogio_Lorenzetti_-_Effects_of_Good_Government_in_the_city_-_Google_Art_Project.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/70/San_Miniato_al_Monte_%28Florence%29_-_Spinello_Aretino_fresco_1.JPG/1280px-San_Miniato_al_Monte_%28Florence%29_-_Spinello_Aretino_fresco_1.JPG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ambrogio</t>
+          <t>Spinello</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LORENZETTI</t>
+          <t>ARETINO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>environ 1290</t>
+          <t>environ 1350</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1338-1339</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sienne</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Palazzo Pubblico</t>
+          <t>Église San Miniato al Monte</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Sacristie</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>"Allégorie et effets du Bon et du Mauvais Gouvernement"</t>
+          <t>"Vie de saint Benoît"</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>"Allegoria ed effetti del Buono e del Cattivo Governo"</t>
+          <t>"Storie di san Benedetto"</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -711,52 +716,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Museo_di_santa_maria_novella%2C_cappellone_degli_spagnoli%2C_affreschi_di_andrea_di_bonaiuto_8.JPG/1280px-Museo_di_santa_maria_novella%2C_cappellone_degli_spagnoli%2C_affreschi_di_andrea_di_bonaiuto_8.JPG</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a7/Melchior_Broederlam_004.jpg/1280px-Melchior_Broederlam_004.jpg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Melchior</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>da FIRENZE</t>
+          <t>BROEDERLAM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1365-1368</t>
+          <t>1393-1399</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Église Santa Maria Novella</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Chapelle des Espagnols</t>
+          <t>Musée des Beaux-Arts</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>"Le Triomphe de saint Thomas d'Aquin"</t>
+          <t>"Retable de Champmol"</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fresque</t>
+          <t>Tempera sur bois</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>belge</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -766,67 +766,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/8_Andrea_di_Cione_Orcagna%2C_Strozzi_Altarpiece._1354-57%2C_Santa_Maria_Novella%2C_Florence..jpeg/1280px-8_Andrea_di_Cione_Orcagna%2C_Strozzi_Altarpiece._1354-57%2C_Santa_Maria_Novella%2C_Florence..jpeg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/48/Last_Judgement_-_Cavallini_-_Santa_Cecilia_01.jpg/1280px-Last_Judgement_-_Cavallini_-_Santa_Cecilia_01.jpg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>di CIONE</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ORCAGNA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ORCAGNA</t>
+          <t>CAVALLINI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>environ 1308</t>
+          <t>environ 1240</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>environ 1330</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1354-1357</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Église Santa Maria Novella</t>
+          <t>Église Santa Cecilia in Trastevere</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>"Retable Strozzi"</t>
+          <t>"Le Jugement dernier"</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>"Pala Strozzi"</t>
+          <t>"Giudizio Universale"</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tempera sur bois</t>
+          <t>Fresque</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -841,32 +831,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Bernardo_Dadd_1347i%2C_MAdone_de_Orsanmichele.jpg/960px-Bernardo_Dadd_1347i%2C_MAdone_de_Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bernardo</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Cimabue_-_Maest%C3%A0_di_Santa_Trinita_-_Google_Art_Project.jpg/1280px-Cimabue_-_Maest%C3%A0_di_Santa_Trinita_-_Google_Art_Project.jpg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DADDI</t>
+          <t>CIMABUE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>environ 1280</t>
+          <t>environ 1240</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1290-1300</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -876,22 +861,32 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Église Orsanmichele</t>
+          <t>Galerie des Offices</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>"Vierge à l'Enfant en trône (Madone d'Orsanmichele)"</t>
+          <t>"Vierge en Majesté de Santa Trinita"</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>"Madonna d'Orsanmichele"</t>
+          <t>"Maestà di Santa Trinita"</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tempera sur bois</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>385 cm</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>223 cm</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -906,27 +901,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Cimabue_-_Maest%C3%A0_di_Santa_Trinita_-_Google_Art_Project.jpg/1280px-Cimabue_-_Maest%C3%A0_di_Santa_Trinita_-_Google_Art_Project.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Museo_di_santa_maria_novella%2C_cappellone_degli_spagnoli%2C_affreschi_di_andrea_di_bonaiuto_8.JPG/1280px-Museo_di_santa_maria_novella%2C_cappellone_degli_spagnoli%2C_affreschi_di_andrea_di_bonaiuto_8.JPG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CIMABUE</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>environ 1240</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1302</t>
+          <t>da FIRENZE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1290-1300</t>
+          <t>1365-1368</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -936,32 +926,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Galerie des Offices</t>
+          <t>Église Santa Maria Novella</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Chapelle des Espagnols</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>"Vierge en Majesté de Santa Trinita"</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>"Maestà di Santa Trinita"</t>
+          <t>"Le Triomphe de saint Thomas d'Aquin"</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tempera sur bois</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>385 cm</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>223 cm</t>
+          <t>Fresque</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -976,62 +956,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/Duccio_Maest%C3%A0.jpg/1280px-Duccio_Maest%C3%A0.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Tommaso_da_modena%2C_ritratti_di_domenicani_%28il_cardinale_di_rouen%29_1352_150cm%2C_treviso%2C_ex_convento_di_san_niccol%C3%B2%2C_sala_del_capitolo.jpg/1280px-Tommaso_da_modena%2C_ritratti_di_domenicani_%28il_cardinale_di_rouen%29_1352_150cm%2C_treviso%2C_ex_convento_di_san_niccol%C3%B2%2C_sala_del_capitolo.jpg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Duccio</t>
+          <t>Tommaso</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>di BUONINSEGNA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>DUCCIO</t>
+          <t>da MODENA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>environ 1255</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>environ 1318</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1308-1311</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sienne</t>
+          <t>Trévise</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Museo dell'Opera del Duomo</t>
+          <t>Séminaire San Nicolò</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>"La Vierge en Majesté"</t>
+          <t>"Portrait du cardinal Hugues de Saint-Cher"</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>"Maestà"</t>
+          <t>"Ritratto del cardinale Ugo di Saint-Cher"</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tempera sur bois</t>
+          <t>Fresque</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1046,32 +1021,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Giotto_-_Scrovegni_-_-36-_-_Lamentation_%28The_Mourning_of_Christ%29_adj.jpg/1280px-Giotto_-_Scrovegni_-_-36-_-_Lamentation_%28The_Mourning_of_Christ%29_adj.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/68/Padova%2C_basilica_di_Sant%27Antonio_-_Cappella_di_San_Giacomo_-_Affreschi_03.jpg/1280px-Padova%2C_basilica_di_Sant%27Antonio_-_Cappella_di_San_Giacomo_-_Affreschi_03.jpg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Giotto</t>
+          <t>Altichiero</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>di BONDONE</t>
+          <t>da ZEVIO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>environ 1267</t>
+          <t>environ 1330</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>environ 1390</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1304-1306</t>
+          <t>1372-1379</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1081,17 +1056,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Chapelle Scrovegni</t>
+          <t>Basilique Saint-Antoine</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Chapelle San Giacomo</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>"La Lamentation"</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>"Compianto sul Cristo morto"</t>
+          <t>"Fresques"</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1111,57 +1086,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/25/Battistero_Padova_-_00view.jpg/1280px-Battistero_Padova_-_00view.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Bernardo_Dadd_1347i%2C_MAdone_de_Orsanmichele.jpg/960px-Bernardo_Dadd_1347i%2C_MAdone_de_Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Giusto</t>
+          <t>Bernardo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>de' MENABUOI</t>
+          <t>DADDI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>environ 1280</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>environ 1391</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1375-1378</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Padoue</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Baptistère de Padoue</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Coupole du baptistère</t>
+          <t>Église Orsanmichele</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>"Le Couronnement de la Vierge"</t>
+          <t>"Vierge à l'Enfant en trône (Madone d'Orsanmichele)"</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>"Incoronazione della Vergine"</t>
+          <t>"Madonna d'Orsanmichele"</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fresque</t>
+          <t>Tempera sur bois</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1176,72 +1151,62 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f9/Huang_Gongwang._Dwelling_in_the_Fuchun_Mountains._detail._National_Palace_Museum%2C_Taipei.jpg/1280px-Huang_Gongwang._Dwelling_in_the_Fuchun_Mountains._detail._National_Palace_Museum%2C_Taipei.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/25/Battistero_Padova_-_00view.jpg/1280px-Battistero_Padova_-_00view.jpg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gongwang</t>
+          <t>Giusto</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HUANG</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1269</t>
+          <t>de' MENABUOI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>environ 1391</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1347-1350</t>
+          <t>1375-1378</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Padoue</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Musée national du Palais</t>
+          <t>Baptistère de Padoue</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Coupole du baptistère</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>"Habitation dans les monts Fuchun"</t>
+          <t>"Le Couronnement de la Vierge"</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>"Fùchūn Shān Jūtú (富春山居图)"</t>
+          <t>"Incoronazione della Vergine"</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Encre sur papier (rouleau)</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>c.33 cm</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>c.636 cm</t>
+          <t>Fresque</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>chinoise</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U12" t="n">
@@ -1251,57 +1216,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Jaume_Serra_-_Altarpiece_of_the_Virgin_-_Google_Art_Project.jpg/1280px-Jaume_Serra_-_Altarpiece_of_the_Virgin_-_Google_Art_Project.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Giotto_-_Scrovegni_-_-36-_-_Lamentation_%28The_Mourning_of_Christ%29_adj.jpg/1280px-Giotto_-_Scrovegni_-_-36-_-_Lamentation_%28The_Mourning_of_Christ%29_adj.jpg</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jaume</t>
+          <t>Giotto</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SERRA</t>
+          <t>di BONDONE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>environ 1267</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>environ 1389</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1367-1381</t>
+          <t>1304-1306</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Barcelone</t>
+          <t>Padoue</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Museu Nacional d'Art de Catalunya</t>
+          <t>Chapelle Scrovegni</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>"Retable de la Vierge de Sixena"</t>
+          <t>"La Lamentation"</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>"Retaule de la Mare de Déu de Sixena"</t>
+          <t>"Compianto sul Cristo morto"</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tempera sur bois</t>
+          <t>Fresque</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>espagnole</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U13" t="n">
@@ -1311,57 +1281,67 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/4_Jean_Pucelle._Hours_of_Jeanne_d%27Evreux._1325-28%2C_Metropolitan_Museum%2C_New-York.jpg/1280px-4_Jean_Pucelle._Hours_of_Jeanne_d%27Evreux._1325-28%2C_Metropolitan_Museum%2C_New-York.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/Duccio_Maest%C3%A0.jpg/1280px-Duccio_Maest%C3%A0.jpg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Duccio</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PUCELLE</t>
+          <t>di BUONINSEGNA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DUCCIO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>environ 1255</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>environ 1334</t>
+          <t>environ 1318</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1324-1328</t>
+          <t>1308-1311</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Sienne</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art (The Cloisters)</t>
+          <t>Museo dell'Opera del Duomo</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>"L'Annonciation"</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>"Les Heures de Jeanne d'Évreux"</t>
+          <t>"La Vierge en Majesté"</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>"Maestà"</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Enluminure, encre et grisaille sur parchemin</t>
+          <t>Tempera sur bois</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U14" t="n">
@@ -1371,52 +1351,67 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d9/Measta._lippo_memmi%2C_palazzo_comunale_in_san_gimignano.jpg/1280px-Measta._lippo_memmi%2C_palazzo_comunale_in_san_gimignano.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/8_Andrea_di_Cione_Orcagna%2C_Strozzi_Altarpiece._1354-57%2C_Santa_Maria_Novella%2C_Florence..jpeg/1280px-8_Andrea_di_Cione_Orcagna%2C_Strozzi_Altarpiece._1354-57%2C_Santa_Maria_Novella%2C_Florence..jpeg</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lippo</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MEMMI</t>
+          <t>di CIONE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ORCAGNA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ORCAGNA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>environ 1308</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>environ 1356</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1354-1357</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>San Gimignano</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Palazzo Comunale</t>
+          <t>Église Santa Maria Novella</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>"Vierge en Majesté"</t>
+          <t>"Retable Strozzi"</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>"Maestà"</t>
+          <t>"Pala Strozzi"</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fresque</t>
+          <t>Tempera sur bois</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -1431,32 +1426,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/Lorenzo_Monaco_-_Incoronazione_della_Vergine_-_Google_Art_Project.jpg/1280px-Lorenzo_Monaco_-_Incoronazione_della_Vergine_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/0/09/Wga_Nardo_di_Cione_Last_Judgment_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Nardo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>environ 1370</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>environ 1425</t>
+          <t>di CIONE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1351-1357</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1466,22 +1451,27 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Galerie des Offices</t>
+          <t>Église Santa Maria Novella</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Chapelle Strozzi</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>"Le Couronnement de la Vierge"</t>
+          <t>"Le Jugement dernier"</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>"Incoronazione della Vergine"</t>
+          <t>"Giudizio Universale"</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tempera sur bois</t>
+          <t>Fresque</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -1496,57 +1486,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7a/Wilton_diptych.jpg/1280px-Wilton_diptych.jpg</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>MAÎTRE DU DIPTYQUE DE WILTON</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Taddeo_Gaddi%2C_Fresco_cycle_on_the_life_of_the_Virgin%2C_1328-38%3B_Baroncelli_Chapel%2C_Basilica_of_Santa_Croce%2C_Florence_%286%29.jpg/1280px-Taddeo_Gaddi%2C_Fresco_cycle_on_the_life_of_the_Virgin%2C_1328-38%3B_Baroncelli_Chapel%2C_Basilica_of_Santa_Croce%2C_Florence_%286%29.jpg</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Taddeo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GADDI</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>environ 1290</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1366</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1395-1399</t>
+          <t>1328-1338</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>National Gallery</t>
+          <t>Église Santa Croce</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Chapelle Baroncelli</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>"Le Diptyque Wilton"</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>"The Wilton Diptych"</t>
+          <t>"L'Annonce aux bergers"</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tempera sur bois</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>53 cm</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>37 cm</t>
+          <t>Fresque</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U17" t="n">
@@ -1556,47 +1551,72 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a7/Melchior_Broederlam_004.jpg/1280px-Melchior_Broederlam_004.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f9/Huang_Gongwang._Dwelling_in_the_Fuchun_Mountains._detail._National_Palace_Museum%2C_Taipei.jpg/1280px-Huang_Gongwang._Dwelling_in_the_Fuchun_Mountains._detail._National_Palace_Museum%2C_Taipei.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Melchior</t>
+          <t>Gongwang</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BROEDERLAM</t>
+          <t>HUANG</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1354</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1393-1399</t>
+          <t>1347-1350</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Musée des Beaux-Arts</t>
+          <t>Musée national du Palais</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>"Retable de Champmol"</t>
+          <t>"Habitation dans les monts Fuchun"</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>"Fùchūn Shān Jūtú (富春山居图)"</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tempera sur bois</t>
+          <t>Encre sur papier (rouleau)</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>c.33 cm</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>c.636 cm</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>belge</t>
+          <t>chinoise</t>
         </is>
       </c>
       <c r="U18" t="n">
@@ -1606,47 +1626,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/0/09/Wga_Nardo_di_Cione_Last_Judgment_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Ambrogio_Lorenzetti_-_Effects_of_Good_Government_in_the_city_-_Google_Art_Project.jpg/1280px-Ambrogio_Lorenzetti_-_Effects_of_Good_Government_in_the_city_-_Google_Art_Project.jpg</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nardo</t>
+          <t>Ambrogio</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>di CIONE</t>
+          <t>LORENZETTI</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>environ 1290</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1348</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1351-1357</t>
+          <t>1338-1339</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Sienne</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Église Santa Maria Novella</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Chapelle Strozzi</t>
+          <t>Palazzo Pubblico</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>"Le Jugement dernier"</t>
+          <t>"Allégorie et effets du Bon et du Mauvais Gouvernement"</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>"Giudizio Universale"</t>
+          <t>"Allegoria ed effetti del Buono e del Cattivo Governo"</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1666,62 +1691,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/46/Ni_Zan_-_Six_Gentlemen.jpg/1280px-Ni_Zan_-_Six_Gentlemen.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/53/Pietro_Lorenzetti_-_The_Birth_of_Mary_-_WGA13553.jpg/1280px-Pietro_Lorenzetti_-_The_Birth_of_Mary_-_WGA13553.jpg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zan</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>LORENZETTI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>environ 1280</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>environ 1348</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Sienne</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Musée de Shanghai</t>
+          <t>Museo dell'Opera del Duomo</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>"Six gentilshommes"</t>
+          <t>"Naissance de la Vierge"</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>"Liù Jūnzǐ Tú (六君子图)"</t>
+          <t>"Natività della Vergine"</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Encre sur papier</t>
+          <t>Tempera sur bois</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>chinoise</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U20" t="n">
@@ -1731,47 +1756,67 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Pala_feriale_Cristo_passo.jpg/1280px-Pala_feriale_Cristo_passo.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/Simone_Martini_and_Lippo_Memmi_-_Annunciazione_-_Google_Art_Project.jpg/1280px-Simone_Martini_and_Lippo_Memmi_-_Annunciazione_-_Google_Art_Project.jpg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Paolo</t>
+          <t>Simone</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VENEZIANO</t>
+          <t>MARTINI</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>environ 1284</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1344</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Venise</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Basilique Saint-Marc</t>
+          <t>Galerie des Offices</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>"Retable des jours ordinaires"</t>
+          <t>"L'Annonciation avec deux saints"</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>"Pala Feriale"</t>
+          <t>"Annunciazione con due santi"</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tempera sur bois</t>
+          <t>Tempera et or sur bois</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>184 cm</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>210 cm</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -1786,52 +1831,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/48/Last_Judgement_-_Cavallini_-_Santa_Cecilia_01.jpg/1280px-Last_Judgement_-_Cavallini_-_Santa_Cecilia_01.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d9/Measta._lippo_memmi%2C_palazzo_comunale_in_san_gimignano.jpg/1280px-Measta._lippo_memmi%2C_palazzo_comunale_in_san_gimignano.jpg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Lippo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CAVALLINI</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>environ 1240</t>
+          <t>MEMMI</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>environ 1330</t>
+          <t>environ 1356</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>San Gimignano</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Église Santa Cecilia in Trastevere</t>
+          <t>Palazzo Comunale</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>"Le Jugement dernier"</t>
+          <t>"Vierge en Majesté"</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>"Giudizio Universale"</t>
+          <t>"Maestà"</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1851,52 +1891,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/53/Pietro_Lorenzetti_-_The_Birth_of_Mary_-_WGA13553.jpg/1280px-Pietro_Lorenzetti_-_The_Birth_of_Mary_-_WGA13553.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/Lorenzo_Monaco_-_Incoronazione_della_Vergine_-_Google_Art_Project.jpg/1280px-Lorenzo_Monaco_-_Incoronazione_della_Vergine_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LORENZETTI</t>
+          <t>MONACO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>environ 1280</t>
+          <t>environ 1370</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>environ 1348</t>
+          <t>environ 1425</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Sienne</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Museo dell'Opera del Duomo</t>
+          <t>Galerie des Offices</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>"Naissance de la Vierge"</t>
+          <t>"Le Couronnement de la Vierge"</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>"Natività della Vergine"</t>
+          <t>"Incoronazione della Vergine"</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1916,72 +1956,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/Simone_Martini_and_Lippo_Memmi_-_Annunciazione_-_Google_Art_Project.jpg/1280px-Simone_Martini_and_Lippo_Memmi_-_Annunciazione_-_Google_Art_Project.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg/960px-An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Simone</t>
+          <t>Ahmad</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MARTINI</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>environ 1284</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1344</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Galerie des Offices</t>
+          <t>Bibliothèque du Topkapi</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>"L'Annonciation avec deux saints"</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>"Annunciazione con due santi"</t>
+          <t>"Un ange offre une ville au Prophète"</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>"Miraj Nameh"</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tempera et or sur bois</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>184 cm</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>210 cm</t>
+          <t>Encre, couleurs et or sur papier</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>persane</t>
         </is>
       </c>
       <c r="U24" t="n">
@@ -1991,67 +2011,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/70/San_Miniato_al_Monte_%28Florence%29_-_Spinello_Aretino_fresco_1.JPG/1280px-San_Miniato_al_Monte_%28Florence%29_-_Spinello_Aretino_fresco_1.JPG</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/46/Ni_Zan_-_Six_Gentlemen.jpg/1280px-Ni_Zan_-_Six_Gentlemen.jpg</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Spinello</t>
+          <t>Zan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ARETINO</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>environ 1350</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Église San Miniato al Monte</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Sacristie</t>
+          <t>Musée de Shanghai</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>"Vie de saint Benoît"</t>
+          <t>"Six gentilshommes"</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>"Storie di san Benedetto"</t>
+          <t>"Liù Jūnzǐ Tú (六君子图)"</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fresque</t>
+          <t>Encre sur papier</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>chinoise</t>
         </is>
       </c>
       <c r="U25" t="n">
@@ -2061,62 +2076,57 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Taddeo_Gaddi%2C_Fresco_cycle_on_the_life_of_the_Virgin%2C_1328-38%3B_Baroncelli_Chapel%2C_Basilica_of_Santa_Croce%2C_Florence_%286%29.jpg/1280px-Taddeo_Gaddi%2C_Fresco_cycle_on_the_life_of_the_Virgin%2C_1328-38%3B_Baroncelli_Chapel%2C_Basilica_of_Santa_Croce%2C_Florence_%286%29.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/4_Jean_Pucelle._Hours_of_Jeanne_d%27Evreux._1325-28%2C_Metropolitan_Museum%2C_New-York.jpg/1280px-4_Jean_Pucelle._Hours_of_Jeanne_d%27Evreux._1325-28%2C_Metropolitan_Museum%2C_New-York.jpg</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Taddeo</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GADDI</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>environ 1290</t>
+          <t>PUCELLE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>environ 1334</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1328-1338</t>
+          <t>1324-1328</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Église Santa Croce</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Chapelle Baroncelli</t>
+          <t>Metropolitan Museum of Art (The Cloisters)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>"L'Annonce aux bergers"</t>
+          <t>"L'Annonciation"</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>"Les Heures de Jeanne d'Évreux"</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fresque</t>
+          <t>Enluminure, encre et grisaille sur parchemin</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U26" t="n">
@@ -2126,47 +2136,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/Feofan_Grek_-_Madonna_of_Don_Icon_-_WGA22207.jpg/1280px-Feofan_Grek_-_Madonna_of_Don_Icon_-_WGA22207.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Jaume_Serra_-_Altarpiece_of_the_Virgin_-_Google_Art_Project.jpg/1280px-Jaume_Serra_-_Altarpiece_of_the_Virgin_-_Google_Art_Project.jpg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Théophane</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LE GREC</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>environ 1340</t>
+          <t>Jaume</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SERRA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>environ 1410</t>
+          <t>environ 1389</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1382-1395</t>
+          <t>1367-1381</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Moscou</t>
+          <t>Barcelone</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Galerie Tretiakov</t>
+          <t>Museu Nacional d'Art de Catalunya</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>"Icône Notre-Dame du Don"</t>
+          <t>"Retable de la Vierge de Sixena"</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>"Retaule de la Mare de Déu de Sixena"</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2176,7 +2186,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>grecque</t>
+          <t>espagnole</t>
         </is>
       </c>
       <c r="U27" t="n">
@@ -2186,57 +2196,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Tommaso_da_modena%2C_ritratti_di_domenicani_%28il_cardinale_di_rouen%29_1352_150cm%2C_treviso%2C_ex_convento_di_san_niccol%C3%B2%2C_sala_del_capitolo.jpg/1280px-Tommaso_da_modena%2C_ritratti_di_domenicani_%28il_cardinale_di_rouen%29_1352_150cm%2C_treviso%2C_ex_convento_di_san_niccol%C3%B2%2C_sala_del_capitolo.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Pala_feriale_Cristo_passo.jpg/1280px-Pala_feriale_Cristo_passo.jpg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tommaso</t>
+          <t>Paolo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>da MODENA</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>1379</t>
+          <t>VENEZIANO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Trévise</t>
+          <t>Venise</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Séminaire San Nicolò</t>
+          <t>Basilique Saint-Marc</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>"Portrait du cardinal Hugues de Saint-Cher"</t>
+          <t>"Retable des jours ordinaires"</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>"Ritratto del cardinale Ugo di Saint-Cher"</t>
+          <t>"Pala Feriale"</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fresque</t>
+          <t>Tempera sur bois</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">

--- a/quizzes/peinture-14e.xlsx
+++ b/quizzes/peinture-14e.xlsx
@@ -637,12 +637,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>environ 1340</t>
+          <t>1340 environ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>environ 1410</t>
+          <t>1410 environ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>environ 1350</t>
+          <t>1350 environ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>environ 1350</t>
+          <t>1350 environ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>environ 1240</t>
+          <t>1240 environ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>environ 1330</t>
+          <t>1330 environ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>environ 1240</t>
+          <t>1240 environ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>environ 1330</t>
+          <t>1330 environ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>environ 1390</t>
+          <t>1390 environ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>environ 1280</t>
+          <t>1280 environ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>environ 1391</t>
+          <t>1391 environ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>environ 1267</t>
+          <t>1267 environ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>environ 1255</t>
+          <t>1255 environ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>environ 1318</t>
+          <t>1318 environ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>environ 1308</t>
+          <t>1308 environ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>environ 1290</t>
+          <t>1290 environ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>environ 1290</t>
+          <t>1290 environ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1872,12 +1872,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>environ 1280</t>
+          <t>1280 environ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>environ 1348</t>
+          <t>1348 environ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>environ 1284</t>
+          <t>1284 environ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>environ 1356</t>
+          <t>1356 environ</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>environ 1370</t>
+          <t>1370 environ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>environ 1425</t>
+          <t>1425 environ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>environ 1334</t>
+          <t>1334 environ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>environ 1389</t>
+          <t>1389 environ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>environ 1308</t>
+          <t>1308 environ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
